--- a/tracker/IG_Engagement_Tracker.xlsx
+++ b/tracker/IG_Engagement_Tracker.xlsx
@@ -457,17 +457,12 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>DAILY WORKFLOW</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -541,17 +536,12 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -600,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -679,6 +669,291 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PEER</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>@by.mirasoul</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>64.5K</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DX9bmmviTkA/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>for someone who loves to hone the art of planning and time management, there was a time I often</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Productivity/planning peer (time blocking, scheduling). Audience overlap with planwithsama target.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>"Honing the art of planning and time management" hit because it's so easy to make planning the work instead of the support. When you hit those over-scheduled stretches, what's the first signal that tells you it's time to scale back?</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>it's so easy to make planning the work instead of the support. When you are over-scheduled, what's the first signal that tells you it's time to scale back?</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DREAM CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>@balancedwithbee</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4.9K</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DX-s6HBlR0S/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Every working mom's reality looks a little different. Different schedules, different support systems</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>WFH toddler mom, 4.9K followers, posting about working-mom mental load — exact dream-customer profile.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The "different schedules, different support systems" framing is what most generic mom advice misses — it assumes everyone's setup is the same. As a WFH toddler mom, what's the one thing about your day you wish more people understood before they offered productivity advice?</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>The "different schedules, different support systems" is what most generic mom advice misses as it assumes everyone's setup is the same. As a WFH mom, what's the one thing you wish more people understood?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MICRO-INFLUENCER</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>@stephxtech</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>22.2K</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DYDHFkwRsdE/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>It took me way too long to figure out that Claude re-reads your entire conversation from the top</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AI/Claude tips creator, 22K followers — bridges into planwithsama's #aiforwomen #aiproductivity hashtag space.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>The point about Claude re-reading the whole conversation from the top changed how I prompt — most people don't realize they're paying for that round-trip every turn. Have you noticed patterns in when starting fresh actually helps vs. when keeping context wins?</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>most people don't realize the context only grows with each prompt and adds up quickly. Have you noticed patterns where starting new session helps vs. staying in the same chat where the context lives?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FRESH POST</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>@wendafulplanning</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>33.5K</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DX7QekwlOy0/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Low energy weeks and high energy weeks do not get the same plan from me. And that's actually why</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Posted yesterday (May 7) — algo still pushing. Energy-based planning content is on-niche.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The "low energy weeks and high energy weeks don't get the same plan" rule is the missing piece in most weekly templates — they assume one default mode. How do you decide which mode you're in on Sunday night, gut feel or a quick check-in?</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>The "low energy weeks and high energy weeks don't get the same plan" concept is the missing piece in most weekly planning videos — they show one default mode. do you let your gut decide or is it more deliberate?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AESTHETIC MATCH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>@becoming.mahya</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.7K</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DXhk-mjTxc4/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>You thought the next title or the next raise would feel different. It doesn't. Pick the life</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Personal-branding/mindset/AI founder energy at 3.7K — warm intentional voice that fits planwithsama's vibe references.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>The "next title or next raise would feel different" line is the trap that keeps so many ambitious women stuck. When you pick the life instead of the title, what's the first thing you find yourself saying no to that you used to say yes to?</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>The "next title or next raise would feel different" line is the trap that keeps so many ambitious women stuck. what's the first thing you find yourself saying no to that you used to say yes to?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -690,7 +965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -756,6 +1031,230 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>@by.mirasoul</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PEER</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DX9bmmviTkA/</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>"Honing the art of planning and time management" hit because it's so easy to make planning the work instead of the support. When you hit those over-scheduled stretches, what's the first signal that tells you it's time to scale back?</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>it's so easy to make planning the work instead of the support. When you are over-scheduled, what's the first signal that tells you it's time to scale back?</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>@balancedwithbee</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DREAM CUSTOMER</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DX-s6HBlR0S/</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>The "different schedules, different support systems" framing is what most generic mom advice misses — it assumes everyone's setup is the same. As a WFH toddler mom, what's the one thing about your day you wish more people understood before they offered productivity advice?</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The "different schedules, different support systems" is what most generic mom advice misses as it assumes everyone's setup is the same. As a WFH mom, what's the one thing you wish more people understood?</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>@stephxtech</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MICRO-INFLUENCER</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DYDHFkwRsdE/</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The point about Claude re-reading the whole conversation from the top changed how I prompt — most people don't realize they're paying for that round-trip every turn. Have you noticed patterns in when starting fresh actually helps vs. when keeping context wins?</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>most people don't realize the context only grows with each prompt and adds up quickly. Have you noticed patterns where starting new session helps vs. staying in the same chat where the context lives?</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>@wendafulplanning</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FRESH POST</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DX7QekwlOy0/</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The "low energy weeks and high energy weeks don't get the same plan" rule is the missing piece in most weekly templates — they assume one default mode. How do you decide which mode you're in on Sunday night, gut feel or a quick check-in?</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>The "low energy weeks and high energy weeks don't get the same plan" concept is the missing piece in most weekly planning videos — they show one default mode. do you let your gut decide or is it more deliberate?</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Creator reply: On it! I just dropped the guide in your messages. (+ DM sent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>@becoming.mahya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AESTHETIC MATCH</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DXhk-mjTxc4/</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>The "next title or next raise would feel different" line is the trap that keeps so many ambitious women stuck. When you pick the life instead of the title, what's the first thing you find yourself saying no to that you used to say yes to?</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>The "next title or next raise would feel different" line is the trap that keeps so many ambitious women stuck. what's the first thing you find yourself saying no to that you used to say yes to?</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -823,20 +1322,14 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>VIBE REFERENCE ACCOUNTS</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>@amandarachlee</t>
@@ -844,7 +1337,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>@nabela</t>
@@ -852,16 +1344,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>@thehomeedit</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -869,10 +1356,8 @@
           <t>HASHTAGS</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>#planwithsama</t>
@@ -880,7 +1365,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>#mentalload</t>
@@ -888,7 +1372,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>#aiforwomen</t>
@@ -896,7 +1379,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>#womenproductivity</t>
@@ -904,7 +1386,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>#sundayreset</t>
@@ -912,7 +1393,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>#planwithme2026</t>
@@ -920,7 +1400,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>#aiproductivity</t>
@@ -928,7 +1407,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>#workingmom</t>
@@ -936,7 +1414,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>#digitalplanner</t>
@@ -944,7 +1421,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>#weeklyplanning</t>
@@ -952,7 +1428,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>#womenwholead</t>
@@ -960,7 +1435,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>#secondshift</t>
@@ -968,7 +1442,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>#productivitytools</t>
@@ -976,7 +1449,6 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>#aiplanning</t>
@@ -984,16 +1456,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>#overwhelmedmom</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1001,7 +1468,6 @@
           <t>BUCKETS</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">

--- a/tracker/IG_Engagement_Tracker.xlsx
+++ b/tracker/IG_Engagement_Tracker.xlsx
@@ -672,7 +672,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -682,54 +682,39 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>@by.mirasoul</t>
+          <t>@tarakermiet</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>64.5K</t>
+          <t>87.3K</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DX9bmmviTkA/</t>
+          <t>https://www.instagram.com/p/DX-fLPFDaHv/</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>for someone who loves to hone the art of planning and time management, there was a time I often</t>
+          <t>There are 292 ways to redesign your current job. Most people try the same 3 and then</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Productivity/planning peer (time blocking, scheduling). Audience overlap with planwithsama target.</t>
+          <t>Burnout + Career Coach, productivity/career-craft peer. Audience overlap with planwithsama mental-load / women-at-work space.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>"Honing the art of planning and time management" hit because it's so easy to make planning the work instead of the support. When you hit those over-scheduled stretches, what's the first signal that tells you it's time to scale back?</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>it's so easy to make planning the work instead of the support. When you are over-scheduled, what's the first signal that tells you it's time to scale back?</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>most people quit before the menu gets long enough to find a real fit. when someone has already done the obvious stuff like delegating and saying no, which crafting type do you usually point them to next?</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -739,54 +724,39 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>@balancedwithbee</t>
+          <t>@theworkingmomroutine</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.9K</t>
+          <t>3.1K</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DX-s6HBlR0S/</t>
+          <t>https://www.instagram.com/p/DYHaZNwEQrp/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Every working mom's reality looks a little different. Different schedules, different support systems</t>
+          <t>Working moms, I know there's a LOT here to unpack. But this is your reminder that you</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>WFH toddler mom, 4.9K followers, posting about working-mom mental load — exact dream-customer profile.</t>
+          <t>3.1K working-mom creator posting about Maycember overwhelm and one-system simplification — bullseye dream-customer profile for planwithsama.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The "different schedules, different support systems" framing is what most generic mom advice misses — it assumes everyone's setup is the same. As a WFH toddler mom, what's the one thing about your day you wish more people understood before they offered productivity advice?</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>The "different schedules, different support systems" is what most generic mom advice misses as it assumes everyone's setup is the same. As a WFH mom, what's the one thing you wish more people understood?</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>one system, one notes app, one calendar input is the opposite of every working mom take that tells us to add more. out of the maycember list, which one tends to fall through the cracks first for you?</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -794,56 +764,16 @@
           <t>MICRO-INFLUENCER</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>@stephxtech</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>22.2K</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/reel/DYDHFkwRsdE/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>It took me way too long to figure out that Claude re-reads your entire conversation from the top</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AI/Claude tips creator, 22K followers — bridges into planwithsama's #aiforwomen #aiproductivity hashtag space.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>The point about Claude re-reading the whole conversation from the top changed how I prompt — most people don't realize they're paying for that round-trip every turn. Have you noticed patterns in when starting fresh actually helps vs. when keeping context wins?</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>most people don't realize the context only grows with each prompt and adds up quickly. Have you noticed patterns where starting new session helps vs. staying in the same chat where the context lives?</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>No pick today — none of the 7 URLs in the pool sit in the 10K–50K follower band.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -853,54 +783,39 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>@wendafulplanning</t>
+          <t>@iampascio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>33.5K</t>
+          <t>59K</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DX7QekwlOy0/</t>
+          <t>https://www.instagram.com/p/DYH_blOltS4/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Low energy weeks and high energy weeks do not get the same plan from me. And that's actually why</t>
+          <t>Your Notion workspace probably looks like a junk drawer right now. Pages everywhere, no</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Posted yesterday (May 7) — algo still pushing. Energy-based planning content is on-niche.</t>
+          <t>Posted 1 day ago — algo still pushing. Notion productivity content is on-niche for planwithsama planner audience.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>The "low energy weeks and high energy weeks don't get the same plan" rule is the missing piece in most weekly templates — they assume one default mode. How do you decide which mode you're in on Sunday night, gut feel or a quick check-in?</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>The "low energy weeks and high energy weeks don't get the same plan" concept is the missing piece in most weekly planning videos — they show one default mode. do you let your gut decide or is it more deliberate?</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>pages everywhere and stuff you haven't opened in months is exactly what mine looks like before a clean. when a workspace has been neglected for a year, do you archive aggressively or rebuild from scratch?</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -910,47 +825,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>@becoming.mahya</t>
+          <t>@kamanabhaskaran</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.7K</t>
+          <t>260K</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DXhk-mjTxc4/</t>
+          <t>https://www.instagram.com/reel/DYFVbwcOUgh/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>You thought the next title or the next raise would feel different. It doesn't. Pick the life</t>
+          <t>Moms, how are we building AI skills to stay relevant and get ahead? For me, the first</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personal-branding/mindset/AI founder energy at 3.7K — warm intentional voice that fits planwithsama's vibe references.</t>
+          <t>Moms + AI skills is the exact center of planwithsama's #aiforwomen niche. Warm intentional tone, polished visual feel.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>The "next title or next raise would feel different" line is the trap that keeps so many ambitious women stuck. When you pick the life instead of the title, what's the first thing you find yourself saying no to that you used to say yes to?</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>The "next title or next raise would feel different" line is the trap that keeps so many ambitious women stuck. what's the first thing you find yourself saying no to that you used to say yes to?</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>deciding which course is the easy part, finding time to actually take it is the real bottleneck. when you carve out the time, is it 20-minute pockets between everything else or one bigger block on a weekend?</t>
         </is>
       </c>
     </row>
@@ -1073,8 +973,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1117,8 +1020,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1161,8 +1067,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1205,7 +1114,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Creator reply: On it! I just dropped the guide in your messages. (+ DM sent)</t>
@@ -1253,8 +1166,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tracker/IG_Engagement_Tracker.xlsx
+++ b/tracker/IG_Engagement_Tracker.xlsx
@@ -672,7 +672,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -682,178 +682,121 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>@tarakermiet</t>
+          <t>@suneeramadhani</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>87.3K</t>
+          <t>~mid-tier (verified founder)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DX-fLPFDaHv/</t>
+          <t>https://www.instagram.com/p/DXzAR5XjnoE/?img_index=2&amp;igsh=MXh2MmQ1eXRrem9zdg==</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>There are 292 ways to redesign your current job. Most people try the same 3 and then</t>
+          <t>Every founder I've ever met says the same thing when I talk about building systems. I don't have time...</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Burnout + Career Coach, productivity/career-craft peer. Audience overlap with planwithsama mental-load / women-at-work space.</t>
+          <t>Verified founder talking about systems vs. busy — productivity-adjacent audience overlap</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>most people quit before the menu gets long enough to find a real fit. when someone has already done the obvious stuff like delegating and saying no, which crafting type do you usually point them to next?</t>
+          <t>The paying-it-back-with-interest line just stopped me. Which of the three did you ignore the longest before you finally built the system?</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DREAM CUSTOMER</t>
+          <t>MICRO-INFLUENCER</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>@theworkingmomroutine</t>
+          <t>@tobieelynn</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.1K</t>
+          <t>~50K-150K (est)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DYHaZNwEQrp/</t>
+          <t>https://www.instagram.com/reel/DXrDfx4Do8T/?igsh=ajdtZnB3bm9ndzJ4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Working moms, I know there's a LOT here to unpack. But this is your reminder that you</t>
+          <t>Something I keep coming back to: if there's flexibility in your job, you don't need to overthink...</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.1K working-mom creator posting about Maycember overwhelm and one-system simplification — bullseye dream-customer profile for planwithsama.</t>
+          <t>Mid-tier working mom creator; in-niche voice, big enough for profile visits, small enough to reply</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>one system, one notes app, one calendar input is the opposite of every working mom take that tells us to add more. out of the maycember list, which one tends to fall through the cracks first for you?</t>
+          <t>The just-a-job reframe at the end hit. How long did it take you to stop filling open hours out of guilt?</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MICRO-INFLUENCER</t>
+          <t>AESTHETIC MATCH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>@allie.williams.advisory</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>~small (founder, in beta)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DX_0p1Rg6hP/?igsh=bmt6NnM5amoydjRh</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Can you hop on a quick sync at 5? My kid gets picked up at 4:30. The old version of me...</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No pick today — none of the 7 URLs in the pool sit in the 10K–50K follower band.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>FRESH POST</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>@iampascio</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>59K</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DYH_blOltS4/</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Your Notion workspace probably looks like a junk drawer right now. Pages everywhere, no</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Posted 1 day ago — algo still pushing. Notion productivity content is on-niche for planwithsama planner audience.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>pages everywhere and stuff you haven't opened in months is exactly what mine looks like before a clean. when a workspace has been neglected for a year, do you archive aggressively or rebuild from scratch?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AESTHETIC MATCH</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>@kamanabhaskaran</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>260K</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/reel/DYFVbwcOUgh/</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Moms, how are we building AI skills to stay relevant and get ahead? For me, the first</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Moms + AI skills is the exact center of planwithsama's #aiforwomen niche. Warm intentional tone, polished visual feel.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>deciding which course is the easy part, finding time to actually take it is the real bottleneck. when you carve out the time, is it 20-minute pockets between everything else or one bigger block on a weekend?</t>
-        </is>
-      </c>
-    </row>
+          <t>Warm intentional founder energy; Career Re-Entry for High-Performing Mothers — matches planwithsama aesthetic</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>The two-line response with no apology is the part I want to internalize. Do you find yourself slipping back to explanations when a senior leader asks?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -865,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1169,6 +1112,132 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>@suneeramadhani</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PEER</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXzAR5XjnoE/?img_index=2&amp;igsh=MXh2MmQ1eXRrem9zdg==</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>The paying-it-back-with-interest line just stopped me. Which of the three did you ignore the longest before you finally built the system?</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Building system take time. Not having it costs money. I known I am going to he paying-it-back-with-interest. For someone starting out on their founder journey what would you say they should focus on first of the three you suggested?</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>@tobieelynn</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MICRO-INFLUENCER</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DXrDfx4Do8T/?igsh=ajdtZnB3bm9ndzJ4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>The just-a-job reframe at the end hit. How long did it take you to stop filling open hours out of guilt?</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The just-a-job reframe at the end hits home. It a conversation I keeping having with my partner and friends. How do you start to make peace with it and get over the work anxiety?</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>@allie.williams.advisory</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AESTHETIC MATCH</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DX_0p1Rg6hP/?igsh=bmt6NnM5amoydjRh</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The two-line response with no apology is the part I want to internalize. Do you find yourself slipping back to explanations when a senior leader asks?</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>two-line response with no apology is the part I want to get comfortable with. Do you find yourself slipping back to explanations when a senior leader asks especially when layoffs are always in season?</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
